--- a/AAII_Financials/Quarterly/HTLM_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/HTLM_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="381" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="463" uniqueCount="92">
   <si>
     <t>HTLM</t>
   </si>
@@ -662,13 +662,10 @@
     <col min="1" max="1" width="7.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="14" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="14" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="15" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
@@ -690,19 +687,19 @@
         <v>46022</v>
       </c>
       <c r="E7" s="2">
-        <v>45838</v>
+        <v>45657</v>
       </c>
       <c r="F7" s="2">
-        <v>45747</v>
+        <v>45473</v>
       </c>
       <c r="G7" s="2">
-        <v>45657</v>
-      </c>
-      <c r="H7" s="2">
-        <v>45473</v>
-      </c>
-      <c r="I7" s="2">
         <v>45382</v>
+      </c>
+      <c r="H7" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="I7" s="2" t="s">
+        <v>3</v>
       </c>
       <c r="J7" s="2" t="s">
         <v>3</v>
@@ -728,19 +725,19 @@
         <v>102800</v>
       </c>
       <c r="E8" s="3">
-        <v>90400</v>
+        <v>96100</v>
       </c>
       <c r="F8" s="3">
-        <v>90400</v>
+        <v>78200</v>
       </c>
       <c r="G8" s="3">
-        <v>96100</v>
-      </c>
-      <c r="H8" s="3">
         <v>78200</v>
       </c>
-      <c r="I8" s="3">
-        <v>78200</v>
+      <c r="H8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I8" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="J8" s="3" t="s">
         <v>3</v>
@@ -766,19 +763,19 @@
         <v>73600</v>
       </c>
       <c r="E9" s="3">
-        <v>65500</v>
+        <v>73900</v>
       </c>
       <c r="F9" s="3">
-        <v>65500</v>
+        <v>57200</v>
       </c>
       <c r="G9" s="3">
-        <v>73900</v>
-      </c>
-      <c r="H9" s="3">
         <v>57200</v>
       </c>
-      <c r="I9" s="3">
-        <v>57200</v>
+      <c r="H9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I9" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="J9" s="3" t="s">
         <v>3</v>
@@ -804,19 +801,19 @@
         <v>29200</v>
       </c>
       <c r="E10" s="3">
-        <v>24900</v>
+        <v>22100</v>
       </c>
       <c r="F10" s="3">
-        <v>24900</v>
+        <v>21000</v>
       </c>
       <c r="G10" s="3">
-        <v>22100</v>
-      </c>
-      <c r="H10" s="3">
         <v>21000</v>
       </c>
-      <c r="I10" s="3">
-        <v>21000</v>
+      <c r="H10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I10" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="J10" s="3" t="s">
         <v>3</v>
@@ -933,11 +930,11 @@
       <c r="D14" s="3">
         <v>-100</v>
       </c>
-      <c r="E14" s="3">
-        <v>-700</v>
-      </c>
-      <c r="F14" s="3">
-        <v>-700</v>
+      <c r="E14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="G14" s="3" t="s">
         <v>3</v>
@@ -975,10 +972,10 @@
         <v>100</v>
       </c>
       <c r="F15" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="G15" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="H15" s="3">
         <v>0</v>
@@ -1023,19 +1020,19 @@
         <v>97100</v>
       </c>
       <c r="E17" s="3">
-        <v>85500</v>
+        <v>93900</v>
       </c>
       <c r="F17" s="3">
-        <v>85500</v>
+        <v>74300</v>
       </c>
       <c r="G17" s="3">
-        <v>93900</v>
-      </c>
-      <c r="H17" s="3">
         <v>74300</v>
       </c>
-      <c r="I17" s="3">
-        <v>74300</v>
+      <c r="H17" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I17" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="J17" s="3" t="s">
         <v>3</v>
@@ -1061,19 +1058,19 @@
         <v>5700</v>
       </c>
       <c r="E18" s="3">
-        <v>4900</v>
+        <v>2200</v>
       </c>
       <c r="F18" s="3">
-        <v>4900</v>
+        <v>3900</v>
       </c>
       <c r="G18" s="3">
-        <v>2200</v>
-      </c>
-      <c r="H18" s="3">
         <v>3900</v>
       </c>
-      <c r="I18" s="3">
-        <v>3900</v>
+      <c r="H18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I18" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="J18" s="3" t="s">
         <v>3</v>
@@ -1115,19 +1112,19 @@
         <v>1200</v>
       </c>
       <c r="E20" s="3">
-        <v>-900</v>
+        <v>800</v>
       </c>
       <c r="F20" s="3">
-        <v>-900</v>
+        <v>200</v>
       </c>
       <c r="G20" s="3">
-        <v>800</v>
-      </c>
-      <c r="H20" s="3">
         <v>200</v>
       </c>
-      <c r="I20" s="3">
-        <v>200</v>
+      <c r="H20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I20" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="J20" s="3" t="s">
         <v>3</v>
@@ -1153,19 +1150,19 @@
         <v>4600</v>
       </c>
       <c r="E21" s="3">
-        <v>5900</v>
+        <v>1400</v>
       </c>
       <c r="F21" s="3">
-        <v>5900</v>
+        <v>3700</v>
       </c>
       <c r="G21" s="3">
-        <v>1400</v>
+        <v>3700</v>
       </c>
       <c r="H21" s="3">
-        <v>3700</v>
+        <v>0</v>
       </c>
       <c r="I21" s="3">
-        <v>3700</v>
+        <v>0</v>
       </c>
       <c r="J21" s="3">
         <v>0</v>
@@ -1191,19 +1188,19 @@
         <v>400</v>
       </c>
       <c r="E22" s="3">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="F22" s="3">
-        <v>400</v>
+        <v>200</v>
       </c>
       <c r="G22" s="3">
-        <v>300</v>
-      </c>
-      <c r="H22" s="3">
         <v>200</v>
       </c>
-      <c r="I22" s="3">
-        <v>200</v>
+      <c r="H22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="J22" s="3" t="s">
         <v>3</v>
@@ -1229,19 +1226,19 @@
         <v>4200</v>
       </c>
       <c r="E23" s="3">
-        <v>6200</v>
+        <v>1100</v>
       </c>
       <c r="F23" s="3">
-        <v>6200</v>
+        <v>3500</v>
       </c>
       <c r="G23" s="3">
-        <v>1100</v>
-      </c>
-      <c r="H23" s="3">
         <v>3500</v>
       </c>
-      <c r="I23" s="3">
-        <v>3500</v>
+      <c r="H23" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I23" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="J23" s="3" t="s">
         <v>3</v>
@@ -1267,19 +1264,19 @@
         <v>800</v>
       </c>
       <c r="E24" s="3">
-        <v>1200</v>
+        <v>400</v>
       </c>
       <c r="F24" s="3">
-        <v>1200</v>
+        <v>800</v>
       </c>
       <c r="G24" s="3">
-        <v>400</v>
-      </c>
-      <c r="H24" s="3">
         <v>800</v>
       </c>
-      <c r="I24" s="3">
-        <v>800</v>
+      <c r="H24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I24" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="J24" s="3" t="s">
         <v>3</v>
@@ -1343,19 +1340,19 @@
         <v>3400</v>
       </c>
       <c r="E26" s="3">
-        <v>5000</v>
+        <v>700</v>
       </c>
       <c r="F26" s="3">
-        <v>5000</v>
+        <v>2700</v>
       </c>
       <c r="G26" s="3">
-        <v>700</v>
-      </c>
-      <c r="H26" s="3">
         <v>2700</v>
       </c>
-      <c r="I26" s="3">
-        <v>2700</v>
+      <c r="H26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I26" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="J26" s="3" t="s">
         <v>3</v>
@@ -1381,19 +1378,19 @@
         <v>3400</v>
       </c>
       <c r="E27" s="3">
-        <v>5000</v>
+        <v>700</v>
       </c>
       <c r="F27" s="3">
-        <v>5000</v>
+        <v>2700</v>
       </c>
       <c r="G27" s="3">
-        <v>700</v>
-      </c>
-      <c r="H27" s="3">
         <v>2700</v>
       </c>
-      <c r="I27" s="3">
-        <v>2700</v>
+      <c r="H27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I27" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="J27" s="3" t="s">
         <v>3</v>
@@ -1571,19 +1568,19 @@
         <v>-1200</v>
       </c>
       <c r="E32" s="3">
-        <v>900</v>
+        <v>-800</v>
       </c>
       <c r="F32" s="3">
-        <v>900</v>
+        <v>-200</v>
       </c>
       <c r="G32" s="3">
-        <v>-800</v>
-      </c>
-      <c r="H32" s="3">
         <v>-200</v>
       </c>
-      <c r="I32" s="3">
-        <v>-200</v>
+      <c r="H32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I32" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="J32" s="3" t="s">
         <v>3</v>
@@ -1609,19 +1606,19 @@
         <v>3400</v>
       </c>
       <c r="E33" s="3">
-        <v>5000</v>
+        <v>700</v>
       </c>
       <c r="F33" s="3">
-        <v>5000</v>
+        <v>2700</v>
       </c>
       <c r="G33" s="3">
-        <v>700</v>
-      </c>
-      <c r="H33" s="3">
         <v>2700</v>
       </c>
-      <c r="I33" s="3">
-        <v>2700</v>
+      <c r="H33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I33" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="J33" s="3" t="s">
         <v>3</v>
@@ -1685,19 +1682,19 @@
         <v>3400</v>
       </c>
       <c r="E35" s="3">
-        <v>5000</v>
+        <v>700</v>
       </c>
       <c r="F35" s="3">
-        <v>5000</v>
+        <v>2700</v>
       </c>
       <c r="G35" s="3">
-        <v>700</v>
-      </c>
-      <c r="H35" s="3">
         <v>2700</v>
       </c>
-      <c r="I35" s="3">
-        <v>2700</v>
+      <c r="H35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I35" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="J35" s="3" t="s">
         <v>3</v>
@@ -1728,19 +1725,19 @@
         <v>46022</v>
       </c>
       <c r="E38" s="2">
-        <v>45838</v>
+        <v>45657</v>
       </c>
       <c r="F38" s="2">
-        <v>45747</v>
+        <v>45473</v>
       </c>
       <c r="G38" s="2">
-        <v>45657</v>
-      </c>
-      <c r="H38" s="2">
-        <v>45473</v>
-      </c>
-      <c r="I38" s="2">
         <v>45382</v>
+      </c>
+      <c r="H38" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="I38" s="2" t="s">
+        <v>3</v>
       </c>
       <c r="J38" s="2" t="s">
         <v>3</v>
@@ -1798,13 +1795,13 @@
         <v>27300</v>
       </c>
       <c r="E41" s="3">
-        <v>20100</v>
-      </c>
-      <c r="F41" s="3">
-        <v>20100</v>
-      </c>
-      <c r="G41" s="3">
         <v>24900</v>
+      </c>
+      <c r="F41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G41" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H41" s="3" t="s">
         <v>3</v>
@@ -1836,13 +1833,13 @@
         <v>5900</v>
       </c>
       <c r="E42" s="3">
-        <v>7200</v>
+        <v>5100</v>
       </c>
       <c r="F42" s="3">
-        <v>7200</v>
+        <v>0</v>
       </c>
       <c r="G42" s="3">
-        <v>5100</v>
+        <v>0</v>
       </c>
       <c r="H42" s="3">
         <v>0</v>
@@ -1874,13 +1871,13 @@
         <v>76000</v>
       </c>
       <c r="E43" s="3">
-        <v>71700</v>
-      </c>
-      <c r="F43" s="3">
-        <v>71700</v>
-      </c>
-      <c r="G43" s="3">
         <v>66900</v>
+      </c>
+      <c r="F43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G43" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H43" s="3" t="s">
         <v>3</v>
@@ -1912,13 +1909,13 @@
         <v>9600</v>
       </c>
       <c r="E44" s="3">
-        <v>10600</v>
-      </c>
-      <c r="F44" s="3">
-        <v>10600</v>
-      </c>
-      <c r="G44" s="3">
         <v>8000</v>
+      </c>
+      <c r="F44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H44" s="3" t="s">
         <v>3</v>
@@ -1950,13 +1947,13 @@
         <v>7000</v>
       </c>
       <c r="E45" s="3">
-        <v>5000</v>
-      </c>
-      <c r="F45" s="3">
-        <v>5000</v>
-      </c>
-      <c r="G45" s="3">
         <v>2800</v>
+      </c>
+      <c r="F45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G45" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H45" s="3" t="s">
         <v>3</v>
@@ -1988,13 +1985,13 @@
         <v>125800</v>
       </c>
       <c r="E46" s="3">
-        <v>114500</v>
-      </c>
-      <c r="F46" s="3">
-        <v>114500</v>
-      </c>
-      <c r="G46" s="3">
         <v>107800</v>
+      </c>
+      <c r="F46" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G46" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H46" s="3" t="s">
         <v>3</v>
@@ -2064,13 +2061,13 @@
         <v>11700</v>
       </c>
       <c r="E48" s="3">
-        <v>11800</v>
-      </c>
-      <c r="F48" s="3">
-        <v>11800</v>
-      </c>
-      <c r="G48" s="3">
         <v>10400</v>
+      </c>
+      <c r="F48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G48" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H48" s="3" t="s">
         <v>3</v>
@@ -2110,11 +2107,11 @@
       <c r="G49" s="3">
         <v>0</v>
       </c>
-      <c r="H49" s="3">
-        <v>0</v>
-      </c>
-      <c r="I49" s="3">
-        <v>0</v>
+      <c r="H49" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I49" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="J49" s="3" t="s">
         <v>3</v>
@@ -2292,13 +2289,13 @@
         <v>139200</v>
       </c>
       <c r="E54" s="3">
-        <v>127100</v>
-      </c>
-      <c r="F54" s="3">
-        <v>127100</v>
-      </c>
-      <c r="G54" s="3">
         <v>118800</v>
+      </c>
+      <c r="F54" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G54" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H54" s="3" t="s">
         <v>3</v>
@@ -2362,13 +2359,13 @@
         <v>79400</v>
       </c>
       <c r="E57" s="3">
-        <v>58100</v>
-      </c>
-      <c r="F57" s="3">
-        <v>58100</v>
-      </c>
-      <c r="G57" s="3">
         <v>75400</v>
+      </c>
+      <c r="F57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G57" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H57" s="3" t="s">
         <v>3</v>
@@ -2400,19 +2397,19 @@
         <v>12300</v>
       </c>
       <c r="E58" s="3">
-        <v>25700</v>
+        <v>17400</v>
       </c>
       <c r="F58" s="3">
-        <v>25700</v>
+        <v>0</v>
       </c>
       <c r="G58" s="3">
-        <v>17400</v>
-      </c>
-      <c r="H58" s="3">
-        <v>0</v>
-      </c>
-      <c r="I58" s="3">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="H58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I58" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="J58" s="3" t="s">
         <v>3</v>
@@ -2438,13 +2435,13 @@
         <v>7600</v>
       </c>
       <c r="E59" s="3">
-        <v>9000</v>
-      </c>
-      <c r="F59" s="3">
-        <v>9000</v>
-      </c>
-      <c r="G59" s="3">
         <v>5700</v>
+      </c>
+      <c r="F59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G59" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H59" s="3" t="s">
         <v>3</v>
@@ -2476,13 +2473,13 @@
         <v>105400</v>
       </c>
       <c r="E60" s="3">
-        <v>99300</v>
-      </c>
-      <c r="F60" s="3">
-        <v>99300</v>
-      </c>
-      <c r="G60" s="3">
         <v>102900</v>
+      </c>
+      <c r="F60" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G60" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H60" s="3" t="s">
         <v>3</v>
@@ -2514,13 +2511,13 @@
         <v>5600</v>
       </c>
       <c r="E61" s="3">
-        <v>5300</v>
+        <v>4900</v>
       </c>
       <c r="F61" s="3">
-        <v>5300</v>
+        <v>0</v>
       </c>
       <c r="G61" s="3">
-        <v>4900</v>
+        <v>0</v>
       </c>
       <c r="H61" s="3">
         <v>0</v>
@@ -2554,11 +2551,11 @@
       <c r="E62" s="3">
         <v>300</v>
       </c>
-      <c r="F62" s="3">
-        <v>300</v>
-      </c>
-      <c r="G62" s="3">
-        <v>300</v>
+      <c r="F62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G62" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H62" s="3" t="s">
         <v>3</v>
@@ -2704,13 +2701,13 @@
         <v>111300</v>
       </c>
       <c r="E66" s="3">
-        <v>105000</v>
-      </c>
-      <c r="F66" s="3">
-        <v>105000</v>
-      </c>
-      <c r="G66" s="3">
         <v>108100</v>
+      </c>
+      <c r="F66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G66" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H66" s="3" t="s">
         <v>3</v>
@@ -2910,13 +2907,13 @@
         <v>2800</v>
       </c>
       <c r="E72" s="3">
-        <v>-3800</v>
-      </c>
-      <c r="F72" s="3">
-        <v>-3800</v>
-      </c>
-      <c r="G72" s="3">
         <v>-13800</v>
+      </c>
+      <c r="F72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G72" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H72" s="3" t="s">
         <v>3</v>
@@ -3062,13 +3059,13 @@
         <v>27800</v>
       </c>
       <c r="E76" s="3">
-        <v>22100</v>
-      </c>
-      <c r="F76" s="3">
-        <v>22100</v>
-      </c>
-      <c r="G76" s="3">
         <v>10700</v>
+      </c>
+      <c r="F76" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G76" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H76" s="3" t="s">
         <v>3</v>
@@ -3143,19 +3140,19 @@
         <v>46022</v>
       </c>
       <c r="E80" s="2">
-        <v>45838</v>
+        <v>45657</v>
       </c>
       <c r="F80" s="2">
-        <v>45747</v>
+        <v>45473</v>
       </c>
       <c r="G80" s="2">
-        <v>45657</v>
-      </c>
-      <c r="H80" s="2">
-        <v>45473</v>
-      </c>
-      <c r="I80" s="2">
         <v>45382</v>
+      </c>
+      <c r="H80" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="I80" s="2" t="s">
+        <v>3</v>
       </c>
       <c r="J80" s="2" t="s">
         <v>3</v>
@@ -3181,19 +3178,19 @@
         <v>3400</v>
       </c>
       <c r="E81" s="3">
-        <v>5000</v>
+        <v>700</v>
       </c>
       <c r="F81" s="3">
-        <v>5000</v>
+        <v>2700</v>
       </c>
       <c r="G81" s="3">
-        <v>700</v>
-      </c>
-      <c r="H81" s="3">
         <v>2700</v>
       </c>
-      <c r="I81" s="3">
-        <v>2700</v>
+      <c r="H81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I81" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="J81" s="3" t="s">
         <v>3</v>
@@ -3231,11 +3228,11 @@
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="D83" s="3">
-        <v>500</v>
-      </c>
-      <c r="E83" s="3">
-        <v>500</v>
+      <c r="D83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E83" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="F83" s="3" t="s">
         <v>3</v>
@@ -3463,19 +3460,19 @@
         <v>9400</v>
       </c>
       <c r="E89" s="3">
-        <v>-5600</v>
+        <v>-1600</v>
       </c>
       <c r="F89" s="3">
-        <v>-5600</v>
+        <v>-6000</v>
       </c>
       <c r="G89" s="3">
-        <v>-1600</v>
-      </c>
-      <c r="H89" s="3">
         <v>-6000</v>
       </c>
-      <c r="I89" s="3">
-        <v>-6000</v>
+      <c r="H89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I89" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="J89" s="3" t="s">
         <v>3</v>
@@ -3517,19 +3514,19 @@
         <v>-1100</v>
       </c>
       <c r="E91" s="3">
-        <v>-300</v>
+        <v>-500</v>
       </c>
       <c r="F91" s="3">
-        <v>-300</v>
+        <v>-200</v>
       </c>
       <c r="G91" s="3">
-        <v>-500</v>
-      </c>
-      <c r="H91" s="3">
         <v>-200</v>
       </c>
-      <c r="I91" s="3">
-        <v>-200</v>
+      <c r="H91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I91" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="J91" s="3" t="s">
         <v>3</v>
@@ -3631,19 +3628,19 @@
         <v>-1600</v>
       </c>
       <c r="E94" s="3">
-        <v>-300</v>
+        <v>0</v>
       </c>
       <c r="F94" s="3">
-        <v>-300</v>
+        <v>-200</v>
       </c>
       <c r="G94" s="3">
-        <v>0</v>
-      </c>
-      <c r="H94" s="3">
         <v>-200</v>
       </c>
-      <c r="I94" s="3">
-        <v>-200</v>
+      <c r="H94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I94" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="J94" s="3" t="s">
         <v>3</v>
@@ -3684,14 +3681,14 @@
       <c r="D96" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E96" s="3" t="s">
-        <v>3</v>
+      <c r="E96" s="3">
+        <v>11800</v>
       </c>
       <c r="F96" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G96" s="3">
-        <v>11800</v>
+      <c r="G96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H96" s="3" t="s">
         <v>3</v>
@@ -3837,19 +3834,19 @@
         <v>-1900</v>
       </c>
       <c r="E100" s="3">
-        <v>3000</v>
+        <v>-5800</v>
       </c>
       <c r="F100" s="3">
-        <v>3000</v>
+        <v>4500</v>
       </c>
       <c r="G100" s="3">
-        <v>-5800</v>
-      </c>
-      <c r="H100" s="3">
         <v>4500</v>
       </c>
-      <c r="I100" s="3">
-        <v>4500</v>
+      <c r="H100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I100" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="J100" s="3" t="s">
         <v>3</v>
@@ -3871,11 +3868,11 @@
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="D101" s="3">
-        <v>-400</v>
-      </c>
-      <c r="E101" s="3">
-        <v>-400</v>
+      <c r="D101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="F101" s="3" t="s">
         <v>3</v>
@@ -3913,19 +3910,19 @@
         <v>5500</v>
       </c>
       <c r="E102" s="3">
-        <v>-2400</v>
+        <v>-8300</v>
       </c>
       <c r="F102" s="3">
-        <v>-2400</v>
+        <v>-2100</v>
       </c>
       <c r="G102" s="3">
-        <v>-8300</v>
+        <v>-2100</v>
       </c>
       <c r="H102" s="3">
-        <v>-2100</v>
+        <v>0</v>
       </c>
       <c r="I102" s="3">
-        <v>-2100</v>
+        <v>0</v>
       </c>
       <c r="J102" s="3">
         <v>0</v>
